--- a/customers/reza.xlsx
+++ b/customers/reza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="246">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -754,6 +754,9 @@
   </si>
   <si>
     <t>جمع کل حساب با احتساب آخرین فاکتور :</t>
+  </si>
+  <si>
+    <t>1405/04/18</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1309,7 @@
       </c>
       <c r="H2" s="8">
         <f>B210</f>
-        <v>3340000</v>
+        <v>4475000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4300,17 +4303,23 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="7">
         <f t="shared" si="8"/>
-        <v>3340000</v>
-      </c>
-      <c r="B204" s="7"/>
+        <v>4475000</v>
+      </c>
+      <c r="B204" s="7">
+        <v>1135000</v>
+      </c>
       <c r="C204" s="7"/>
-      <c r="D204" s="7"/>
-      <c r="E204" s="1"/>
+      <c r="D204" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="7">
         <f t="shared" si="8"/>
-        <v>3340000</v>
+        <v>4475000</v>
       </c>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
@@ -4320,7 +4329,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <f t="shared" si="8"/>
-        <v>3340000</v>
+        <v>4475000</v>
       </c>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
@@ -4330,7 +4339,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <f t="shared" si="8"/>
-        <v>3340000</v>
+        <v>4475000</v>
       </c>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -4340,7 +4349,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <f t="shared" si="8"/>
-        <v>3340000</v>
+        <v>4475000</v>
       </c>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -4351,7 +4360,7 @@
       <c r="A209" s="8"/>
       <c r="B209" s="8">
         <f xml:space="preserve"> SUM(B188:B208)+B183</f>
-        <v>20014000</v>
+        <v>21149000</v>
       </c>
       <c r="C209" s="8">
         <f>SUM(C188:C208)+C183</f>
@@ -4363,7 +4372,7 @@
       <c r="A210" s="8"/>
       <c r="B210" s="12">
         <f>A208</f>
-        <v>3340000</v>
+        <v>4475000</v>
       </c>
       <c r="C210" s="18" t="s">
         <v>244</v>

--- a/customers/reza.xlsx
+++ b/customers/reza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="247">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -757,6 +757,9 @@
   </si>
   <si>
     <t>1405/04/18</t>
+  </si>
+  <si>
+    <t>1405/04/19</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1312,7 @@
       </c>
       <c r="H2" s="8">
         <f>B210</f>
-        <v>4475000</v>
+        <v>3475000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4319,17 +4322,23 @@
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="7">
         <f t="shared" si="8"/>
-        <v>4475000</v>
+        <v>3475000</v>
       </c>
       <c r="B205" s="7"/>
-      <c r="C205" s="7"/>
-      <c r="D205" s="7"/>
-      <c r="E205" s="1"/>
+      <c r="C205" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <f t="shared" si="8"/>
-        <v>4475000</v>
+        <v>3475000</v>
       </c>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
@@ -4339,7 +4348,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <f t="shared" si="8"/>
-        <v>4475000</v>
+        <v>3475000</v>
       </c>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -4349,7 +4358,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <f t="shared" si="8"/>
-        <v>4475000</v>
+        <v>3475000</v>
       </c>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -4364,7 +4373,7 @@
       </c>
       <c r="C209" s="8">
         <f>SUM(C188:C208)+C183</f>
-        <v>16674000</v>
+        <v>17674000</v>
       </c>
       <c r="D209" s="8"/>
     </row>
@@ -4372,7 +4381,7 @@
       <c r="A210" s="8"/>
       <c r="B210" s="12">
         <f>A208</f>
-        <v>4475000</v>
+        <v>3475000</v>
       </c>
       <c r="C210" s="18" t="s">
         <v>244</v>

--- a/customers/reza.xlsx
+++ b/customers/reza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="248">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -760,6 +760,9 @@
   </si>
   <si>
     <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>1405/06/05</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1315,7 @@
       </c>
       <c r="H2" s="8">
         <f>B210</f>
-        <v>3475000</v>
+        <v>3610000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4338,17 +4341,23 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <f t="shared" si="8"/>
-        <v>3475000</v>
-      </c>
-      <c r="B206" s="7"/>
+        <v>3610000</v>
+      </c>
+      <c r="B206" s="7">
+        <v>135000</v>
+      </c>
       <c r="C206" s="7"/>
-      <c r="D206" s="7"/>
-      <c r="E206" s="1"/>
+      <c r="D206" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <f t="shared" si="8"/>
-        <v>3475000</v>
+        <v>3610000</v>
       </c>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -4358,7 +4367,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <f t="shared" si="8"/>
-        <v>3475000</v>
+        <v>3610000</v>
       </c>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -4369,7 +4378,7 @@
       <c r="A209" s="8"/>
       <c r="B209" s="8">
         <f xml:space="preserve"> SUM(B188:B208)+B183</f>
-        <v>21149000</v>
+        <v>21284000</v>
       </c>
       <c r="C209" s="8">
         <f>SUM(C188:C208)+C183</f>
@@ -4381,7 +4390,7 @@
       <c r="A210" s="8"/>
       <c r="B210" s="12">
         <f>A208</f>
-        <v>3475000</v>
+        <v>3610000</v>
       </c>
       <c r="C210" s="18" t="s">
         <v>244</v>

--- a/customers/reza.xlsx
+++ b/customers/reza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="247">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -760,9 +760,6 @@
   </si>
   <si>
     <t>1405/04/19</t>
-  </si>
-  <si>
-    <t>1405/06/05</t>
   </si>
 </sst>
 </file>
@@ -1315,7 +1312,7 @@
       </c>
       <c r="H2" s="8">
         <f>B210</f>
-        <v>3610000</v>
+        <v>3475000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4341,23 +4338,17 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <f t="shared" si="8"/>
-        <v>3610000</v>
-      </c>
-      <c r="B206" s="7">
-        <v>135000</v>
-      </c>
+        <v>3475000</v>
+      </c>
+      <c r="B206" s="7"/>
       <c r="C206" s="7"/>
-      <c r="D206" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="D206" s="7"/>
+      <c r="E206" s="1"/>
     </row>
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <f t="shared" si="8"/>
-        <v>3610000</v>
+        <v>3475000</v>
       </c>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -4367,7 +4358,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <f t="shared" si="8"/>
-        <v>3610000</v>
+        <v>3475000</v>
       </c>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -4378,7 +4369,7 @@
       <c r="A209" s="8"/>
       <c r="B209" s="8">
         <f xml:space="preserve"> SUM(B188:B208)+B183</f>
-        <v>21284000</v>
+        <v>21149000</v>
       </c>
       <c r="C209" s="8">
         <f>SUM(C188:C208)+C183</f>
@@ -4390,7 +4381,7 @@
       <c r="A210" s="8"/>
       <c r="B210" s="12">
         <f>A208</f>
-        <v>3610000</v>
+        <v>3475000</v>
       </c>
       <c r="C210" s="18" t="s">
         <v>244</v>
